--- a/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_BOUNDARY_GUARDRAILS_PER_SEMESTER.xlsx
+++ b/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_BOUNDARY_GUARDRAILS_PER_SEMESTER.xlsx
@@ -8289,7 +8289,7 @@
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>ML statistik / neural network / deep learning (STI-413/STI-626); agen otonom &amp; MAS (STA-602).</t>
+          <t>ML statistik / neural network / deep learning (STI-413/STI-726); agen otonom &amp; MAS (STA-602).</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B651" s="8" t="inlineStr">
         <is>
-          <t>PyTorch/TensorFlow, CNN/RNN, deep learning (STI-626); sistem otonom BDI &amp; teori permainan (STA-602).</t>
+          <t>PyTorch/TensorFlow, CNN/RNN, deep learning (STI-726); sistem otonom BDI &amp; teori permainan (STA-602).</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="B652" s="7" t="inlineStr">
         <is>
-          <t>Pemodelan data tabular klasik; menyerahkan data tak terstruktur (citra/sekuensial) ke STI-626.</t>
+          <t>Pemodelan data tabular klasik; menyerahkan data tak terstruktur (citra/sekuensial) ke STI-726.</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="B804" s="8" t="inlineStr">
         <is>
-          <t>Layout CSS/HTML (STI-311); message broker skala besar (STI-627); frontend mobile (STI-522).</t>
+          <t>Layout CSS/HTML (STI-311); message broker skala besar (STI-727); frontend mobile (STI-522).</t>
         </is>
       </c>
     </row>
@@ -18276,7 +18276,7 @@
       </c>
       <c r="B805" s="7" t="inlineStr">
         <is>
-          <t>Layanan backend modular; menyerahkan aksesibilitas mobile ke STI-522 dan skalabilitas terdistribusi ke STI-627.</t>
+          <t>Layanan backend modular; menyerahkan aksesibilitas mobile ke STI-522 dan skalabilitas terdistribusi ke STI-727.</t>
         </is>
       </c>
     </row>
@@ -26013,7 +26013,7 @@
     <row r="1158" ht="20" customHeight="1">
       <c r="A1158" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B1158" s="4" t="n"/>
@@ -26098,7 +26098,7 @@
     <row r="1166" ht="20" customHeight="1">
       <c r="A1166" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B1166" s="4" t="n"/>
@@ -26221,7 +26221,7 @@
     <row r="1173" ht="20" customHeight="1">
       <c r="A1173" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B1173" s="4" t="n"/>
@@ -26432,7 +26432,7 @@
     <row r="1184" ht="20" customHeight="1">
       <c r="A1184" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B1184" s="4" t="n"/>
@@ -27075,7 +27075,7 @@
     <row r="1203" ht="20" customHeight="1">
       <c r="A1203" s="3" t="inlineStr">
         <is>
-          <t>24. STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>24. STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B1203" s="4" t="n"/>
@@ -27116,7 +27116,7 @@
       </c>
       <c r="B1206" s="8" t="inlineStr">
         <is>
-          <t>Riset/training arsitektur deep learning dari nol (STI-626); pengaturan lifecycle MLOps penuh &amp; CI/CD/CT (STA-701).</t>
+          <t>Riset/training arsitektur deep learning dari nol (STI-726); pengaturan lifecycle MLOps penuh &amp; CI/CD/CT (STA-701).</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27136,7 @@
     <row r="1209" ht="20" customHeight="1">
       <c r="A1209" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B1209" s="4" t="n"/>
@@ -27221,7 +27221,7 @@
     <row r="1217" ht="20" customHeight="1">
       <c r="A1217" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B1217" s="4" t="n"/>
@@ -27344,7 +27344,7 @@
     <row r="1224" ht="20" customHeight="1">
       <c r="A1224" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B1224" s="4" t="n"/>
@@ -27555,7 +27555,7 @@
     <row r="1235" ht="20" customHeight="1">
       <c r="A1235" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B1235" s="4" t="n"/>
@@ -28198,7 +28198,7 @@
     <row r="1254" ht="20" customHeight="1">
       <c r="A1254" s="3" t="inlineStr">
         <is>
-          <t>25. STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>25. STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B1254" s="4" t="n"/>
@@ -28259,7 +28259,7 @@
     <row r="1260" ht="20" customHeight="1">
       <c r="A1260" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B1260" s="4" t="n"/>
@@ -28344,7 +28344,7 @@
     <row r="1268" ht="20" customHeight="1">
       <c r="A1268" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B1268" s="4" t="n"/>
@@ -28467,7 +28467,7 @@
     <row r="1275" ht="20" customHeight="1">
       <c r="A1275" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B1275" s="4" t="n"/>
@@ -28678,7 +28678,7 @@
     <row r="1286" ht="20" customHeight="1">
       <c r="A1286" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B1286" s="4" t="n"/>
@@ -29321,7 +29321,7 @@
     <row r="1305" ht="20" customHeight="1">
       <c r="A1305" s="3" t="inlineStr">
         <is>
-          <t>26. STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>26. STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B1305" s="4" t="n"/>
@@ -29382,7 +29382,7 @@
     <row r="1311" ht="20" customHeight="1">
       <c r="A1311" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B1311" s="4" t="n"/>
@@ -29467,7 +29467,7 @@
     <row r="1319" ht="20" customHeight="1">
       <c r="A1319" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B1319" s="4" t="n"/>
@@ -29590,7 +29590,7 @@
     <row r="1326" ht="20" customHeight="1">
       <c r="A1326" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B1326" s="4" t="n"/>
@@ -29801,7 +29801,7 @@
     <row r="1337" ht="20" customHeight="1">
       <c r="A1337" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B1337" s="4" t="n"/>
@@ -30444,7 +30444,7 @@
     <row r="1356" ht="20" customHeight="1">
       <c r="A1356" s="3" t="inlineStr">
         <is>
-          <t>27. STI-627 — Digital Platform Engineering</t>
+          <t>27. STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B1356" s="4" t="n"/>
@@ -30558,7 +30558,7 @@
       </c>
       <c r="B1366" s="7" t="inlineStr">
         <is>
-          <t>STI-627, MKU-204</t>
+          <t>STI-727, MKU-204</t>
         </is>
       </c>
     </row>
@@ -31608,7 +31608,7 @@
       </c>
       <c r="B1410" s="8" t="inlineStr">
         <is>
-          <t>Implementasi teknis deep learning/MVP rekayasa (STI-626/STI-627); desain UI (STI-308).</t>
+          <t>Implementasi teknis deep learning/MVP rekayasa (STI-726/STI-727); desain UI (STI-308).</t>
         </is>
       </c>
     </row>
@@ -35902,7 +35902,7 @@
       </c>
       <c r="B1605" s="8" t="inlineStr">
         <is>
-          <t>Metode numerik klasik (Bisection, Newton-Raphson, Spline, Romberg, RK4); melatih CNN/RNN penuh (STI-626); dashboard BI relasional semata (STI-415).</t>
+          <t>Metode numerik klasik (Bisection, Newton-Raphson, Spline, Romberg, RK4); melatih CNN/RNN penuh (STI-726); dashboard BI relasional semata (STI-415).</t>
         </is>
       </c>
     </row>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="B1656" s="8" t="inlineStr">
         <is>
-          <t>Inferensi sistem pakar rule-based (STI-307); training deep reinforcement learning skala besar (STI-626).</t>
+          <t>Inferensi sistem pakar rule-based (STI-307); training deep reinforcement learning skala besar (STI-726).</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="B1657" s="7" t="inlineStr">
         <is>
-          <t>Agen otonom terdistribusi; menyerahkan NN besar ke STI-626 dan pengambilan keputusan tunggal ke STI-307.</t>
+          <t>Agen otonom terdistribusi; menyerahkan NN besar ke STI-726 dan pengambilan keputusan tunggal ke STI-307.</t>
         </is>
       </c>
     </row>
@@ -38082,7 +38082,7 @@
       </c>
       <c r="B1704" s="8" t="inlineStr">
         <is>
-          <t>Provisi VM &amp; kontainer Docker tunggal (STI-417); arsitektur aplikasi microservices (STI-627).</t>
+          <t>Provisi VM &amp; kontainer Docker tunggal (STI-417); arsitektur aplikasi microservices (STI-727).</t>
         </is>
       </c>
     </row>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="B1705" s="7" t="inlineStr">
         <is>
-          <t>Automasi &amp; orkestrasi infrastruktur; menyerahkan desain aplikasi microservices ke STI-627.</t>
+          <t>Automasi &amp; orkestrasi infrastruktur; menyerahkan desain aplikasi microservices ke STI-727.</t>
         </is>
       </c>
     </row>
@@ -41265,7 +41265,7 @@
       </c>
       <c r="B1849" s="7" t="inlineStr">
         <is>
-          <t>Spesialisasi domain vertikal; menyerahkan infrastruktur platform umum ke STI-627/STC-702.</t>
+          <t>Spesialisasi domain vertikal; menyerahkan infrastruktur platform umum ke STI-727/STC-702.</t>
         </is>
       </c>
     </row>
@@ -41326,7 +41326,7 @@
       </c>
       <c r="B1855" s="7" t="inlineStr">
         <is>
-          <t>STI-413, STI-624</t>
+          <t>STI-413, STI-726</t>
         </is>
       </c>
     </row>
@@ -42310,7 +42310,7 @@
       </c>
       <c r="B1896" s="8" t="inlineStr">
         <is>
-          <t>Riset/training arsitektur model baru (STI-626); deployment layanan inference via FastAPI/ONNX mendalam (STI-624).</t>
+          <t>Riset/training arsitektur model baru (STI-726); deployment layanan inference via FastAPI/ONNX mendalam (STI-726).</t>
         </is>
       </c>
     </row>
@@ -42322,7 +42322,7 @@
       </c>
       <c r="B1897" s="7" t="inlineStr">
         <is>
-          <t>Otomasi &amp; tata kelola model produksi; menyerahkan pembuatan layanan inference ke STI-624.</t>
+          <t>Otomasi &amp; tata kelola model produksi; menyerahkan pembuatan layanan inference ke STI-726.</t>
         </is>
       </c>
     </row>
@@ -43433,7 +43433,7 @@
       </c>
       <c r="B1947" s="8" t="inlineStr">
         <is>
-          <t>Analisis NLP statistik klasik VSM (STI-414); layanan API web kembali (STI-416/STI-624).</t>
+          <t>Analisis NLP statistik klasik VSM (STI-414); layanan API web kembali (STI-416/STI-726).</t>
         </is>
       </c>
     </row>
@@ -43506,7 +43506,7 @@
       </c>
       <c r="B1954" s="7" t="inlineStr">
         <is>
-          <t>STI-626, STI-521</t>
+          <t>STI-726, STI-521</t>
         </is>
       </c>
     </row>
@@ -47727,7 +47727,7 @@
       </c>
       <c r="B2142" s="8" t="inlineStr">
         <is>
-          <t>Blueprint SPBE selesai; fokus pada proyek bisnis sistem informasi (STI-625); pemodelan UML detail (STI-306).</t>
+          <t>Blueprint SPBE selesai; fokus pada proyek bisnis sistem informasi (STI-727); pemodelan UML detail (STI-306).</t>
         </is>
       </c>
     </row>
@@ -47739,7 +47739,7 @@
       </c>
       <c r="B2143" s="7" t="inlineStr">
         <is>
-          <t>Peta arsitektur enterprise korporat; menyerahkan sistem domain publik ke STI-625.</t>
+          <t>Peta arsitektur enterprise korporat; menyerahkan sistem domain publik ke STI-727.</t>
         </is>
       </c>
     </row>
@@ -49841,7 +49841,7 @@
       </c>
       <c r="B2238" s="8" t="inlineStr">
         <is>
-          <t>Membangun microservice event-driven skalabel (STI-627); penyusunan PRD &amp; metrik produk (STC-703).</t>
+          <t>Membangun microservice event-driven skalabel (STI-727); penyusunan PRD &amp; metrik produk (STC-703).</t>
         </is>
       </c>
     </row>
